--- a/alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx
+++ b/alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx
@@ -7887,7 +7887,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8143,7 +8143,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8264,7 +8264,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8385,7 +8385,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8506,7 +8506,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8627,7 +8627,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx
+++ b/alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx
@@ -5294,7 +5294,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -5313,7 +5313,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6127,7 +6127,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6146,7 +6146,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6517,7 +6517,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6536,7 +6536,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6669,7 +6669,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6688,7 +6688,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6753,7 +6753,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6772,7 +6772,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6837,7 +6837,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -6856,7 +6856,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7015,7 +7015,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7034,7 +7034,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7580,7 +7580,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">markets/network/dist/20261023_AI</t>
+      <t xml:space="preserve">markets/network/dist/20261026_AI</t>
     </r>
     <r>
       <rPr>
@@ -7599,7 +7599,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.2.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx
+++ b/alab/dist/20261025_Astera Labs模型_v0.1.1.xlsx
@@ -7868,26 +7868,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8124,26 +8124,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8245,26 +8245,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8366,26 +8366,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8487,26 +8487,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8608,26 +8608,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -39776,7 +39776,7 @@
         <v>30</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>31</v>
@@ -43546,7 +43546,7 @@
       </c>
       <c r="C14" s="20" t="n">
         <f aca="false">PL!D75/itc_26</f>
-        <v>0.00240865358021204</v>
+        <v>0.00240865358021205</v>
       </c>
       <c r="D14" s="20" t="n">
         <f aca="false">PL!E75/itc_27</f>
